--- a/data/trans_orig/P1434-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1434-Edad-trans_orig.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>5004</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>5004</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -989,7 +989,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>729548</t>
+          <t>730485</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>729548</t>
+          <t>730485</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5520</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5520</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>633148</t>
+          <t>631887</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>633148</t>
+          <t>631887</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>856</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11427</t>
+          <t>10288</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>856</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11427</t>
+          <t>10288</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>507720</t>
+          <t>508859</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>518229</t>
+          <t>518291</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>507720</t>
+          <t>508859</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>518229</t>
+          <t>518291</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12352</t>
+          <t>12209</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29476</t>
+          <t>29494</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12352</t>
+          <t>12209</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29476</t>
+          <t>29494</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>357234</t>
+          <t>357216</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>374358</t>
+          <t>374501</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1718,12 +1718,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>357234</t>
+          <t>357216</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>374358</t>
+          <t>374501</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>
@@ -1863,12 +1863,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26573</t>
+          <t>26393</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49978</t>
+          <t>49400</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26573</t>
+          <t>26393</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49978</t>
+          <t>49400</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1913,12 +1913,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,88%</t>
         </is>
       </c>
     </row>
@@ -1941,12 +1941,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>242605</t>
+          <t>243183</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266010</t>
+          <t>266190</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>242605</t>
+          <t>243183</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>266010</t>
+          <t>266190</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1991,12 +1991,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,98%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32902</t>
+          <t>32207</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53795</t>
+          <t>54828</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32902</t>
+          <t>32207</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53795</t>
+          <t>54828</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>26,12%</t>
         </is>
       </c>
     </row>
@@ -2179,12 +2179,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>156088</t>
+          <t>155055</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>176981</t>
+          <t>177676</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2194,12 +2194,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>156088</t>
+          <t>155055</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>176981</t>
+          <t>177676</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,65%</t>
         </is>
       </c>
     </row>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>86266</t>
+          <t>88774</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>127218</t>
+          <t>126899</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>86266</t>
+          <t>88774</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>127218</t>
+          <t>126899</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -2417,12 +2417,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3149325</t>
+          <t>3149644</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3190277</t>
+          <t>3187769</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2432,12 +2432,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3149325</t>
+          <t>3149644</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3190277</t>
+          <t>3187769</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2467,12 +2467,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10776</t>
+          <t>12088</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10776</t>
+          <t>12088</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>671087</t>
+          <t>669775</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>671087</t>
+          <t>669775</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14853</t>
+          <t>13899</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33383</t>
+          <t>31469</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14853</t>
+          <t>13899</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33383</t>
+          <t>31469</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3753,12 +3753,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -3781,12 +3781,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>396046</t>
+          <t>397960</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>414576</t>
+          <t>415530</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>396046</t>
+          <t>397960</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>414576</t>
+          <t>415530</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -3941,12 +3941,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42674</t>
+          <t>41352</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>72092</t>
+          <t>70594</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42674</t>
+          <t>41352</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>72092</t>
+          <t>70594</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>22,79%</t>
         </is>
       </c>
     </row>
@@ -4019,12 +4019,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>237694</t>
+          <t>239192</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>267112</t>
+          <t>268434</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>237694</t>
+          <t>239192</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>267112</t>
+          <t>268434</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,65%</t>
         </is>
       </c>
     </row>
@@ -4179,12 +4179,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32683</t>
+          <t>32096</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57619</t>
+          <t>59105</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32683</t>
+          <t>32096</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>57619</t>
+          <t>59105</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,87%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>190040</t>
+          <t>188554</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>214976</t>
+          <t>215563</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>190040</t>
+          <t>188554</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>214976</t>
+          <t>215563</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>87,04%</t>
         </is>
       </c>
     </row>
@@ -4417,12 +4417,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>102054</t>
+          <t>101960</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>149623</t>
+          <t>147982</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>102054</t>
+          <t>101960</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>149623</t>
+          <t>147982</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -4495,12 +4495,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3274964</t>
+          <t>3276605</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3322533</t>
+          <t>3322627</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3274964</t>
+          <t>3276605</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3322533</t>
+          <t>3322627</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6825</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6825</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>662272</t>
+          <t>662900</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>662272</t>
+          <t>662900</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>990</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10234</t>
+          <t>10620</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>990</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10234</t>
+          <t>10620</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>635814</t>
+          <t>635428</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>645050</t>
+          <t>645058</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>635814</t>
+          <t>635428</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>645050</t>
+          <t>645058</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>6651</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21686</t>
+          <t>21571</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>6651</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21686</t>
+          <t>21571</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -5859,12 +5859,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>456232</t>
+          <t>456347</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>471528</t>
+          <t>471267</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>456232</t>
+          <t>456347</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>471528</t>
+          <t>471267</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -6019,12 +6019,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32142</t>
+          <t>31317</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55800</t>
+          <t>56473</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32142</t>
+          <t>31317</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55800</t>
+          <t>56473</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,89%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>278530</t>
+          <t>277857</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>302188</t>
+          <t>303013</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>278530</t>
+          <t>277857</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>302188</t>
+          <t>303013</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,63%</t>
         </is>
       </c>
     </row>
@@ -6257,12 +6257,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36461</t>
+          <t>37270</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59251</t>
+          <t>59328</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6292,12 +6292,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36461</t>
+          <t>37270</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>59251</t>
+          <t>59328</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6307,12 +6307,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,09%</t>
         </is>
       </c>
     </row>
@@ -6335,12 +6335,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>197747</t>
+          <t>197670</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>220537</t>
+          <t>219728</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>197747</t>
+          <t>197670</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>220537</t>
+          <t>219728</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,5%</t>
         </is>
       </c>
     </row>
@@ -6495,12 +6495,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>92176</t>
+          <t>91109</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>133426</t>
+          <t>131154</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6530,12 +6530,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>92176</t>
+          <t>91109</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>133426</t>
+          <t>131154</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6545,12 +6545,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -6573,12 +6573,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3260924</t>
+          <t>3263196</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3302174</t>
+          <t>3303241</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6608,12 +6608,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3260924</t>
+          <t>3263196</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3302174</t>
+          <t>3303241</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,32%</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>395910</t>
+          <t>404047</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>395910</t>
+          <t>404047</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -7058,17 +7058,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>395910</t>
+          <t>404047</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>395910</t>
+          <t>404047</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>395910</t>
+          <t>404047</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7093,17 +7093,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>395910</t>
+          <t>404047</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>395910</t>
+          <t>404047</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>395910</t>
+          <t>404047</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>422008</t>
+          <t>475141</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -7253,7 +7253,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>422008</t>
+          <t>475141</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -7296,17 +7296,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>422008</t>
+          <t>475141</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>422008</t>
+          <t>475141</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>422008</t>
+          <t>475141</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7331,17 +7331,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>422008</t>
+          <t>475141</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>422008</t>
+          <t>475141</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>422008</t>
+          <t>475141</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8156</t>
+          <t>6831</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8156</t>
+          <t>6831</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -7456,27 +7456,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>532564</t>
+          <t>616872</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>525766</t>
+          <t>611397</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>533922</t>
+          <t>618228</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7491,27 +7491,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>532564</t>
+          <t>616872</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>525766</t>
+          <t>611397</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>533922</t>
+          <t>618228</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7534,17 +7534,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>533922</t>
+          <t>618228</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>533922</t>
+          <t>618228</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>533922</t>
+          <t>618228</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7569,17 +7569,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>533922</t>
+          <t>618228</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>533922</t>
+          <t>618228</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>533922</t>
+          <t>618228</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7616,32 +7616,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10211</t>
+          <t>10289</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20842</t>
+          <t>19335</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7651,32 +7651,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10211</t>
+          <t>10289</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20842</t>
+          <t>19335</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -7694,32 +7694,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>871323</t>
+          <t>683934</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>860692</t>
+          <t>674888</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>878252</t>
+          <t>689017</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7729,32 +7729,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>871323</t>
+          <t>683934</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>860692</t>
+          <t>674888</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>878252</t>
+          <t>689017</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -7772,17 +7772,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>881534</t>
+          <t>694223</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>881534</t>
+          <t>694223</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>881534</t>
+          <t>694223</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7807,17 +7807,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>881534</t>
+          <t>694223</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>881534</t>
+          <t>694223</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>881534</t>
+          <t>694223</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7854,32 +7854,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>27233</t>
+          <t>27615</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18937</t>
+          <t>19137</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37639</t>
+          <t>39004</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7889,32 +7889,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>27233</t>
+          <t>27615</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18937</t>
+          <t>19137</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37639</t>
+          <t>39004</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -7932,32 +7932,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>530647</t>
+          <t>578350</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>520241</t>
+          <t>566961</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>538943</t>
+          <t>586828</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7967,32 +7967,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>530647</t>
+          <t>578350</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>520241</t>
+          <t>566961</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>538943</t>
+          <t>586828</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>
@@ -8010,17 +8010,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>557880</t>
+          <t>605965</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>557880</t>
+          <t>605965</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>557880</t>
+          <t>605965</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8045,17 +8045,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>557880</t>
+          <t>605965</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>557880</t>
+          <t>605965</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>557880</t>
+          <t>605965</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8092,32 +8092,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>59421</t>
+          <t>65202</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48512</t>
+          <t>52820</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>71052</t>
+          <t>78184</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8127,32 +8127,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>59421</t>
+          <t>65202</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48512</t>
+          <t>52820</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>71052</t>
+          <t>78184</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -8170,32 +8170,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>307323</t>
+          <t>340142</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>295692</t>
+          <t>327160</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>318232</t>
+          <t>352524</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8205,32 +8205,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>307323</t>
+          <t>340142</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>295692</t>
+          <t>327160</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>318232</t>
+          <t>352524</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,97%</t>
         </is>
       </c>
     </row>
@@ -8248,17 +8248,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>366744</t>
+          <t>405344</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>366744</t>
+          <t>405344</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>366744</t>
+          <t>405344</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8283,17 +8283,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>366744</t>
+          <t>405344</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>366744</t>
+          <t>405344</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>366744</t>
+          <t>405344</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8330,32 +8330,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>82015</t>
+          <t>88615</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>70453</t>
+          <t>77028</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>94554</t>
+          <t>102860</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8365,32 +8365,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>82015</t>
+          <t>88615</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>70453</t>
+          <t>77028</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>94554</t>
+          <t>102860</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,25%</t>
         </is>
       </c>
     </row>
@@ -8408,32 +8408,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>199998</t>
+          <t>220697</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>187459</t>
+          <t>206452</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>211560</t>
+          <t>232284</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8443,32 +8443,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>199998</t>
+          <t>220697</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>187459</t>
+          <t>206452</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>211560</t>
+          <t>232284</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>75,1%</t>
         </is>
       </c>
     </row>
@@ -8486,17 +8486,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8521,17 +8521,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8568,32 +8568,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>180237</t>
+          <t>193076</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>139447</t>
+          <t>170780</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>204671</t>
+          <t>217408</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8603,32 +8603,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>180237</t>
+          <t>193076</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>139447</t>
+          <t>170780</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>204671</t>
+          <t>217408</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -8646,32 +8646,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3259774</t>
+          <t>3319184</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3235340</t>
+          <t>3294852</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3300564</t>
+          <t>3341480</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8681,32 +8681,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3259774</t>
+          <t>3319184</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3235340</t>
+          <t>3294852</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3300564</t>
+          <t>3341480</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,14%</t>
         </is>
       </c>
     </row>
@@ -8724,17 +8724,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3440011</t>
+          <t>3512260</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3440011</t>
+          <t>3512260</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3440011</t>
+          <t>3512260</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8759,17 +8759,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3440011</t>
+          <t>3512260</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3440011</t>
+          <t>3512260</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3440011</t>
+          <t>3512260</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
